--- a/jira_export_2026-10-19.xlsx
+++ b/jira_export_2026-10-19.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>23,575 €</t>
+          <t>27,857 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,14 +760,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>5,808 €</t>
+          <t>7,056 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>17,767 €</t>
+          <t>20,801 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>333 h</t>
+          <t>339 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -2533,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
         <v>4399.5</v>
       </c>
       <c r="O25" s="16" t="n">
-        <v>0</v>
+        <v>2639.7</v>
       </c>
       <c r="P25" s="12" t="n">
-        <v>0</v>
+        <v>659.92</v>
       </c>
     </row>
     <row r="26">
@@ -2757,10 +2757,10 @@
         <v>1470.38</v>
       </c>
       <c r="O28" s="16" t="n">
-        <v>0</v>
+        <v>238.44</v>
       </c>
       <c r="P28" s="15" t="n">
-        <v>0</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="29">
@@ -3252,11 +3252,11 @@
       <c r="N35" s="12" t="n">
         <v>394</v>
       </c>
-      <c r="O35" s="16" t="n">
-        <v>0</v>
+      <c r="O35" s="12" t="n">
+        <v>394</v>
       </c>
       <c r="P35" s="12" t="n">
-        <v>0</v>
+        <v>131.33</v>
       </c>
     </row>
     <row r="36">
@@ -4245,7 +4245,7 @@
         <v>4</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
@@ -5612,11 +5612,11 @@
       <c r="N68" s="15" t="n">
         <v>400</v>
       </c>
-      <c r="O68" s="16" t="n">
-        <v>0</v>
+      <c r="O68" s="15" t="n">
+        <v>465.85</v>
       </c>
       <c r="P68" s="15" t="n">
-        <v>0</v>
+        <v>62.11</v>
       </c>
     </row>
     <row r="69">
@@ -6333,10 +6333,10 @@
         <v>0</v>
       </c>
       <c r="O78" s="15" t="n">
-        <v>0</v>
+        <v>112.38</v>
       </c>
       <c r="P78" s="15" t="n">
-        <v>0</v>
+        <v>56.19</v>
       </c>
     </row>
     <row r="79">
@@ -6613,10 +6613,10 @@
         <v>337.5</v>
       </c>
       <c r="O82" s="16" t="n">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="P82" s="15" t="n">
-        <v>0</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="83">
@@ -6957,7 +6957,7 @@
         <v>6</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
@@ -7693,10 +7693,10 @@
         <v>910</v>
       </c>
       <c r="O97" s="16" t="n">
-        <v>0</v>
+        <v>318.5</v>
       </c>
       <c r="P97" s="12" t="n">
-        <v>0</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="98">
@@ -12305,10 +12305,10 @@
         <v>121646.717</v>
       </c>
       <c r="O167" s="18" t="n">
-        <v>23575.202</v>
+        <v>27856.572</v>
       </c>
       <c r="P167" s="18" t="n">
-        <v>105.68</v>
+        <v>121.87</v>
       </c>
     </row>
   </sheetData>
@@ -13611,7 +13611,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>154.25</v>
+        <v>154.75</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>18</v>
@@ -13620,7 +13620,7 @@
         <v>7.83</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>180.08</v>
+        <v>180.58</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>26.25</v>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.5%</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13641,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>32.75</v>
+        <v>37.75</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -13650,7 +13650,7 @@
         <v>10.25</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>20.5%</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13672,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>79.33</v>
+        <v>79.83</v>
       </c>
     </row>
   </sheetData>
@@ -13757,22 +13757,22 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>494037</v>
+        <v>489408</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>205185</v>
+        <v>203308</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>288852</v>
+        <v>286100</v>
       </c>
       <c r="E5" s="24" t="n">
         <v>227073</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>16651</v>
+        <v>14011</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>18055</v>
+        <v>17943</v>
       </c>
     </row>
     <row r="6">
@@ -13782,13 +13782,13 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>261098</v>
+        <v>259851</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>69561</v>
+        <v>68425</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>191538</v>
+        <v>191425</v>
       </c>
       <c r="E6" s="25" t="n">
         <v>172214</v>
@@ -13797,7 +13797,7 @@
         <v>9175</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>7624</v>
+        <v>7512</v>
       </c>
     </row>
     <row r="7">
@@ -13807,19 +13807,19 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>229838</v>
+        <v>226458</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>132524</v>
+        <v>131783</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>97314</v>
+        <v>94674</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>54860</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>7476</v>
+        <v>4836</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>10431</v>

--- a/jira_export_2026-10-19.xlsx
+++ b/jira_export_2026-10-19.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>27,857 €</t>
+          <t>28,034 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>20,801 €</t>
+          <t>20,978 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>339 h</t>
+          <t>347 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -4173,7 +4173,7 @@
         <v>3</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="N58" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="15" t="n">
         <v>177.5</v>
-      </c>
-      <c r="O58" s="16" t="n">
-        <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>4</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>15.25</v>
+        <v>15.5</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>1242.9</v>
       </c>
       <c r="P62" s="15" t="n">
-        <v>81.5</v>
+        <v>80.19</v>
       </c>
     </row>
     <row r="63">
@@ -5597,7 +5597,7 @@
         <v>4</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>465.85</v>
       </c>
       <c r="P68" s="15" t="n">
-        <v>62.11</v>
+        <v>58.23</v>
       </c>
     </row>
     <row r="69">
@@ -6597,7 +6597,7 @@
         <v>5</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>112.5</v>
       </c>
       <c r="P82" s="15" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
     </row>
     <row r="83">
@@ -6669,7 +6669,7 @@
         <v>5</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
@@ -12302,13 +12302,13 @@
       <c r="L167" s="17" t="inlineStr"/>
       <c r="M167" s="17" t="inlineStr"/>
       <c r="N167" s="18" t="n">
-        <v>121646.717</v>
+        <v>121469.217</v>
       </c>
       <c r="O167" s="18" t="n">
-        <v>27856.572</v>
+        <v>28034.072</v>
       </c>
       <c r="P167" s="18" t="n">
-        <v>121.87</v>
+        <v>121.05</v>
       </c>
     </row>
   </sheetData>
@@ -12487,7 +12487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -12513,7 +12513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 10 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 11 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -12578,22 +12578,22 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-36327</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
+          <t>[VILLE D'AIGLE] - Ajout MATERIEL</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>VILLE D'AIGLE</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
+          <t>Ajout MATERIEL</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="H5" s="11" t="n">
@@ -12616,12 +12616,12 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35476</t>
+          <t>PDMDEP-36333</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>00180644</t>
+          <t>00184404</t>
         </is>
       </c>
       <c r="K5" s="12" t="n">
@@ -12631,22 +12631,22 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35227</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE CHAUNY] - Migration de GEODP-Placier + Remise en service paiement cb + Pax + Formation </t>
+          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHAUNY</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration de GEODP-Placier + Remise en service paiement cb + Pax + Formation </t>
+          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -12669,12 +12669,12 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35234</t>
+          <t>PDMDEP-35476</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>00179117</t>
+          <t>00180644</t>
         </is>
       </c>
       <c r="K6" s="15" t="n">
@@ -12684,22 +12684,22 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-35227</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t xml:space="preserve">[VILLE DE CHAUNY] - Migration de GEODP-Placier + Remise en service paiement cb + Pax + Formation </t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>VILLE DE CHAUNY</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t xml:space="preserve">Migration de GEODP-Placier + Remise en service paiement cb + Pax + Formation </t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -12722,37 +12722,37 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34294</t>
+          <t>PDMDEP-35234</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>00171435</t>
+          <t>00179117</t>
         </is>
       </c>
       <c r="K7" s="12" t="n">
-        <v>1630</v>
+        <v>815</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -12775,37 +12775,37 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34256</t>
+          <t>PDMDEP-34294</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>00171362</t>
+          <t>00171435</t>
         </is>
       </c>
       <c r="K8" s="15" t="n">
-        <v>815</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="H9" s="11" t="n">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34199</t>
+          <t>PDMDEP-34256</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>00171163</t>
+          <t>00171362</t>
         </is>
       </c>
       <c r="K9" s="12" t="n">
@@ -12843,22 +12843,22 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="H10" s="14" t="n">
@@ -12881,37 +12881,37 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34019</t>
+          <t>PDMDEP-34199</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>00170492</t>
+          <t>00171163</t>
         </is>
       </c>
       <c r="K10" s="15" t="n">
-        <v>1630</v>
+        <v>815</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -12934,37 +12934,37 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33848</t>
+          <t>PDMDEP-34019</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>00161104</t>
+          <t>00170492</t>
         </is>
       </c>
       <c r="K11" s="12" t="n">
-        <v>815</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -12987,12 +12987,12 @@
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33156</t>
+          <t>PDMDEP-33848</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>00165721</t>
+          <t>00161104</t>
         </is>
       </c>
       <c r="K12" s="15" t="n">
@@ -13002,22 +13002,22 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -13040,12 +13040,12 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31819</t>
+          <t>PDMDEP-33156</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>00159472</t>
+          <t>00165721</t>
         </is>
       </c>
       <c r="K13" s="12" t="n">
@@ -13055,22 +13055,22 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31486</t>
+          <t>PDMDEP-31819</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>00157474</t>
+          <t>00159472</t>
         </is>
       </c>
       <c r="K14" s="15" t="n">
@@ -13106,22 +13106,75 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-31479</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE TREGUIER</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31486</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>00157474</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr"/>
-      <c r="C15" s="17" t="inlineStr"/>
-      <c r="D15" s="17" t="inlineStr"/>
-      <c r="E15" s="17" t="inlineStr"/>
-      <c r="F15" s="17" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr"/>
-      <c r="H15" s="17" t="inlineStr"/>
-      <c r="I15" s="17" t="inlineStr"/>
-      <c r="J15" s="17" t="inlineStr"/>
-      <c r="K15" s="18" t="n">
-        <v>9780</v>
+      <c r="B16" s="17" t="inlineStr"/>
+      <c r="C16" s="17" t="inlineStr"/>
+      <c r="D16" s="17" t="inlineStr"/>
+      <c r="E16" s="17" t="inlineStr"/>
+      <c r="F16" s="17" t="inlineStr"/>
+      <c r="G16" s="17" t="inlineStr"/>
+      <c r="H16" s="17" t="inlineStr"/>
+      <c r="I16" s="17" t="inlineStr"/>
+      <c r="J16" s="17" t="inlineStr"/>
+      <c r="K16" s="18" t="n">
+        <v>10595</v>
       </c>
     </row>
   </sheetData>
@@ -13137,6 +13190,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13611,7 +13665,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>154.75</v>
+        <v>157.75</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>18</v>
@@ -13620,17 +13674,17 @@
         <v>7.83</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>180.58</v>
+        <v>183.58</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>26.25</v>
+        <v>29.75</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>508.2</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13726,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>79.83</v>
+        <v>81.83</v>
       </c>
     </row>
   </sheetData>
@@ -13757,16 +13811,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>489408</v>
+        <v>489231</v>
       </c>
       <c r="C5" s="24" t="n">
         <v>203308</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>286100</v>
+        <v>285922</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>227073</v>
+        <v>226896</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>14011</v>
@@ -13807,16 +13861,16 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>226458</v>
+        <v>226280</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>131783</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>94674</v>
+        <v>94497</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>54860</v>
+        <v>54682</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>4836</v>
@@ -14706,7 +14760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -14727,7 +14781,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>5 clôture(s) : 5 projet(s), 0 rework</t>
+          <t>6 clôture(s) : 6 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -14857,17 +14911,17 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34147</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>[Mairie de Vaison la romaine] - Ajout d'une régie et mise en</t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Vaison la romaine</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -14887,59 +14941,89 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-34147</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>[Mairie de Vaison la romaine] - Ajout d'une régie et mise en</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Mairie de Vaison la romaine</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-35261</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>[VILLE DE VILLEURBANNE] - Reprise des données TLPE</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="n">
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="27" t="n">
+      <c r="B13" s="27" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="27" t="n">
         <v>0</v>
       </c>
     </row>
